--- a/Data/EXCEL/Transfer/salemon/202208/6762-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6762-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DC1F53B-9E12-4170-B25D-422D335BCB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31396111-1070-46DA-80F1-AFC9F7C3BFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6762-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,21 +1227,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="10" width="9.5" customWidth="1"/>
-    <col min="11" max="13" width="10.125" customWidth="1"/>
-    <col min="14" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1260,7 +1268,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1299,7 +1307,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1342,7 +1350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1381,7 +1389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1434,7 +1442,7 @@
         <v>-29.8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1487,7 +1495,7 @@
         <v>-33.4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1540,7 +1548,7 @@
         <v>-34.700000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1593,7 +1601,7 @@
         <v>-33</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1646,7 +1654,7 @@
         <v>-32.1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1699,7 +1707,7 @@
         <v>-35.200000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1752,7 +1760,7 @@
         <v>-32.5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1805,7 +1813,7 @@
         <v>-23.9</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1858,7 +1866,7 @@
         <v>-4.1399999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1911,7 +1919,7 @@
         <v>-5.31</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1964,7 +1972,7 @@
         <v>-2.54</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2017,7 +2025,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2070,7 +2078,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2123,7 +2131,7 @@
         <v>9.67</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2176,7 +2184,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2229,7 +2237,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2282,7 +2290,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2335,7 +2343,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2388,7 +2396,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2441,7 +2449,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2494,7 +2502,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2547,7 +2555,7 @@
         <v>44.3</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2600,7 +2608,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2653,7 +2661,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2706,7 +2714,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2759,7 +2767,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2812,7 +2820,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2865,7 +2873,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2918,7 +2926,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2971,7 +2979,7 @@
         <v>58.8</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3024,7 +3032,7 @@
         <v>68.7</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3077,7 +3085,7 @@
         <v>63.2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3130,7 +3138,7 @@
         <v>136.9</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3183,7 +3191,7 @@
         <v>158.1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3236,7 +3244,7 @@
         <v>175.7</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3304,7 +3312,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>